--- a/backend/app/xbrl/india/template.xlsx
+++ b/backend/app/xbrl/india/template.xlsx
@@ -3313,18 +3313,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="585" t="inlineStr">
-        <is>
-          <t>RAMSON &amp; GRANDSON JEWELLERS PVT. LTD. 1-4-20</t>
-        </is>
-      </c>
+      <c r="A1" s="585" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="586" t="inlineStr">
-        <is>
-          <t>CIN: U52393AP2011PTC072492</t>
-        </is>
-      </c>
+      <c r="A2" s="586" t="n"/>
       <c r="B2" s="306" t="n"/>
       <c r="C2" s="306" t="n"/>
     </row>
@@ -3346,11 +3338,7 @@
     </row>
     <row r="5">
       <c r="A5" s="541" t="inlineStr"/>
-      <c r="B5" s="589" t="inlineStr">
-        <is>
-          <t>RAMSON &amp; GRANDSON JEWELLERS PVT. LTD. - (from 1-Apr-2019) - (from 1-Apr-20)</t>
-        </is>
-      </c>
+      <c r="B5" s="589" t="n"/>
       <c r="C5" s="146" t="n"/>
     </row>
     <row r="6">
@@ -3460,29 +3448,17 @@
       <c r="C16" s="559" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="564" t="inlineStr">
-        <is>
-          <t>G. Aruna</t>
-        </is>
-      </c>
+      <c r="A17" s="564" t="n"/>
       <c r="B17" s="549" t="n"/>
       <c r="C17" s="550" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="564" t="inlineStr">
-        <is>
-          <t>G. Krishna</t>
-        </is>
-      </c>
+      <c r="A18" s="564" t="n"/>
       <c r="B18" s="549" t="n"/>
       <c r="C18" s="550" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="560" t="inlineStr">
-        <is>
-          <t>G. Krupan Kumar</t>
-        </is>
-      </c>
+      <c r="A19" s="560" t="n"/>
       <c r="B19" s="549" t="n"/>
       <c r="C19" s="550" t="n"/>
     </row>
@@ -3568,11 +3544,7 @@
       <c r="C28" s="562" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="560" t="inlineStr">
-        <is>
-          <t>O.P. Bang &amp; Co.</t>
-        </is>
-      </c>
+      <c r="A29" s="560" t="n"/>
       <c r="B29" s="549" t="n"/>
       <c r="C29" s="550" t="n"/>
     </row>
@@ -3829,20 +3801,12 @@
       <c r="C57" s="556" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold (Sale)</t>
-        </is>
-      </c>
+      <c r="A58" s="490" t="n"/>
       <c r="B58" s="555" t="n"/>
       <c r="C58" s="556" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="490" t="inlineStr">
-        <is>
-          <t>Pure Silver (Sale)</t>
-        </is>
-      </c>
+      <c r="A59" s="490" t="n"/>
       <c r="B59" s="555" t="n"/>
       <c r="C59" s="556" t="n"/>
     </row>
@@ -3901,29 +3865,17 @@
       <c r="C65" s="555" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold Purchase IGST</t>
-        </is>
-      </c>
+      <c r="A66" s="490" t="n"/>
       <c r="B66" s="556" t="n"/>
       <c r="C66" s="555" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold Purchase Local</t>
-        </is>
-      </c>
+      <c r="A67" s="490" t="n"/>
       <c r="B67" s="556" t="n"/>
       <c r="C67" s="555" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="490" t="inlineStr">
-        <is>
-          <t>Pure Silver Purchase</t>
-        </is>
-      </c>
+      <c r="A68" s="490" t="n"/>
       <c r="B68" s="556" t="n"/>
       <c r="C68" s="555" t="n"/>
     </row>
@@ -4172,11 +4124,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="609" t="inlineStr">
-        <is>
-          <t>RAMSON AND GRANDSON JEWELLERS PRIVATE LIMITED</t>
-        </is>
-      </c>
+      <c r="A1" s="609" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="606" t="inlineStr">
@@ -4678,11 +4626,7 @@
       <c r="F30" s="613" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="242" t="inlineStr">
-        <is>
-          <t>( Firm regn. No. 000383S)</t>
-        </is>
-      </c>
+      <c r="A31" s="242" t="n"/>
       <c r="B31" s="613" t="n"/>
       <c r="C31" s="613" t="n"/>
       <c r="D31" s="261" t="inlineStr">
@@ -4696,30 +4640,18 @@
       <c r="A32" s="242" t="n"/>
       <c r="B32" s="613" t="n"/>
       <c r="C32" s="613" t="n"/>
-      <c r="D32" s="261" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="D32" s="261" t="n"/>
       <c r="F32" s="613" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="242" t="n"/>
       <c r="B33" s="613" t="n"/>
       <c r="C33" s="613" t="n"/>
-      <c r="D33" s="261" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="D33" s="261" t="n"/>
       <c r="F33" s="613" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="242" t="inlineStr">
-        <is>
-          <t>Om Prakash Bang</t>
-        </is>
-      </c>
+      <c r="A34" s="242" t="n"/>
       <c r="B34" s="613" t="n"/>
       <c r="C34" s="613" t="n"/>
       <c r="D34" s="58" t="n"/>
@@ -4741,22 +4673,14 @@
       <c r="F35" s="613" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="242" t="inlineStr">
-        <is>
-          <t>Membership No. 018948</t>
-        </is>
-      </c>
+      <c r="A36" s="242" t="n"/>
       <c r="B36" s="613" t="n"/>
       <c r="C36" s="613" t="n"/>
       <c r="D36" s="261" t="n"/>
       <c r="F36" s="613" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="242" t="inlineStr">
-        <is>
-          <t>Place: Hyderabad</t>
-        </is>
-      </c>
+      <c r="A37" s="242" t="n"/>
       <c r="B37" s="613" t="n"/>
       <c r="C37" s="613" t="n"/>
       <c r="D37" s="261" t="inlineStr">
@@ -4773,22 +4697,14 @@
       </c>
       <c r="B38" s="613" t="n"/>
       <c r="C38" s="613" t="n"/>
-      <c r="D38" s="261" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="D38" s="261" t="n"/>
       <c r="F38" s="613" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="242" t="n"/>
       <c r="B39" s="613" t="n"/>
       <c r="C39" s="613" t="n"/>
-      <c r="D39" s="261" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="D39" s="261" t="n"/>
       <c r="F39" s="613" t="n"/>
     </row>
     <row r="40">
@@ -4877,11 +4793,7 @@
       <c r="M2" s="149" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="614" t="inlineStr">
-        <is>
-          <t>M/S. RAMSON AND GRANDSON JEWELLERS (P) lTD</t>
-        </is>
-      </c>
+      <c r="A3" s="614" t="n"/>
       <c r="L3" s="149" t="n"/>
       <c r="M3" s="149" t="n"/>
     </row>
@@ -6334,11 +6246,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="621" t="inlineStr">
-        <is>
-          <t>RAMSON AND GRANDSON JEWELLERS PRIVATE LIMITED</t>
-        </is>
-      </c>
+      <c r="A1" s="621" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -9023,18 +8931,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="585" t="inlineStr">
-        <is>
-          <t>RAMSON &amp; GRANDSON JEWELLERS PVT. LTD.</t>
-        </is>
-      </c>
+      <c r="A1" s="585" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="586" t="inlineStr">
-        <is>
-          <t>CIN: U52393AP2011PTC072492</t>
-        </is>
-      </c>
+      <c r="A2" s="586" t="n"/>
       <c r="B2" s="306" t="n"/>
       <c r="C2" s="306" t="n"/>
     </row>
@@ -9056,11 +8956,7 @@
     </row>
     <row r="5">
       <c r="A5" s="541" t="inlineStr"/>
-      <c r="B5" s="589" t="inlineStr">
-        <is>
-          <t>RAMSON &amp; GRANDSON JEWELLERS PVT. LTD. - (from 1-4-22)</t>
-        </is>
-      </c>
+      <c r="B5" s="589" t="n"/>
       <c r="C5" s="146" t="n"/>
     </row>
     <row r="6">
@@ -9332,20 +9228,12 @@
       <c r="C34" s="556" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold (Sale)</t>
-        </is>
-      </c>
+      <c r="A35" s="490" t="n"/>
       <c r="B35" s="555" t="n"/>
       <c r="C35" s="556" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="490" t="inlineStr">
-        <is>
-          <t>Pure Silver (Sale)</t>
-        </is>
-      </c>
+      <c r="A36" s="490" t="n"/>
       <c r="B36" s="555" t="n"/>
       <c r="C36" s="556" t="n"/>
     </row>
@@ -9395,29 +9283,17 @@
       <c r="C41" s="555" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold Purchase IGST</t>
-        </is>
-      </c>
+      <c r="A42" s="490" t="n"/>
       <c r="B42" s="556" t="n"/>
       <c r="C42" s="555" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="490" t="inlineStr">
-        <is>
-          <t>Pure Gold Purchase Local</t>
-        </is>
-      </c>
+      <c r="A43" s="490" t="n"/>
       <c r="B43" s="556" t="n"/>
       <c r="C43" s="555" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="490" t="inlineStr">
-        <is>
-          <t>Pure Silver Purchase</t>
-        </is>
-      </c>
+      <c r="A44" s="490" t="n"/>
       <c r="B44" s="556" t="n"/>
       <c r="C44" s="555" t="n"/>
     </row>
@@ -10251,27 +10127,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>( Firm regn. No. 000383S)</t>
-        </is>
-      </c>
       <c r="B30" s="613" t="n"/>
-      <c r="E30" s="282" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="E30" s="282" t="n"/>
       <c r="F30" s="613" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="294" t="n"/>
       <c r="B31" s="613" t="n"/>
-      <c r="E31" s="282" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="E31" s="282" t="n"/>
       <c r="F31" s="282" t="inlineStr">
         <is>
           <t>Director</t>
@@ -10281,25 +10144,12 @@
     <row r="32">
       <c r="B32" s="613" t="n"/>
       <c r="E32" s="282" t="n"/>
-      <c r="F32" s="282" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="F32" s="282" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Om Prakash Bang</t>
-        </is>
-      </c>
       <c r="B33" s="613" t="n"/>
       <c r="E33" s="613" t="n"/>
-      <c r="F33" s="282" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="F33" s="282" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10316,31 +10166,13 @@
       <c r="F34" s="282" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Membership No. 018948</t>
-        </is>
-      </c>
       <c r="B35" s="613" t="n"/>
-      <c r="E35" s="282" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="E35" s="282" t="n"/>
       <c r="F35" s="613" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Place: Hyderabad</t>
-        </is>
-      </c>
       <c r="B36" s="613" t="n"/>
-      <c r="E36" s="282" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="E36" s="282" t="n"/>
       <c r="F36" s="282" t="inlineStr">
         <is>
           <t>Director</t>
@@ -10353,11 +10185,7 @@
         <v/>
       </c>
       <c r="B37" s="613" t="n"/>
-      <c r="F37" s="282" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="F37" s="282" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10366,11 +10194,7 @@
         </is>
       </c>
       <c r="B38" s="613" t="n"/>
-      <c r="F38" s="282" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="F38" s="282" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="539" t="n"/>
@@ -11526,11 +11350,7 @@
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
       <c r="A1" s="322" t="n"/>
-      <c r="B1" s="322" t="inlineStr">
-        <is>
-          <t>RAMSON AND GRANDSON JEWELLERS PRIVATE LIMITED</t>
-        </is>
-      </c>
+      <c r="B1" s="322" t="n"/>
       <c r="C1" s="322" t="n"/>
       <c r="D1" s="322" t="n"/>
       <c r="E1" s="659" t="n"/>
@@ -11801,11 +11621,7 @@
     </row>
     <row r="14" ht="15.5" customHeight="1">
       <c r="A14" s="358" t="n"/>
-      <c r="B14" s="359" t="inlineStr">
-        <is>
-          <t>Aruna Guggila</t>
-        </is>
-      </c>
+      <c r="B14" s="359" t="n"/>
       <c r="C14" s="681">
         <f>E14</f>
         <v/>
@@ -11834,11 +11650,7 @@
     </row>
     <row r="15" ht="15.5" customHeight="1">
       <c r="A15" s="358" t="n"/>
-      <c r="B15" s="365" t="inlineStr">
-        <is>
-          <t>Krishna Guggila</t>
-        </is>
-      </c>
+      <c r="B15" s="365" t="n"/>
       <c r="C15" s="681" t="n"/>
       <c r="D15" s="685" t="n"/>
       <c r="E15" s="681">
@@ -11864,11 +11676,7 @@
     </row>
     <row r="16" ht="15.5" customHeight="1">
       <c r="A16" s="358" t="n"/>
-      <c r="B16" s="365" t="inlineStr">
-        <is>
-          <t>Krupan Guggila</t>
-        </is>
-      </c>
+      <c r="B16" s="365" t="n"/>
       <c r="C16" s="686">
         <f>E16</f>
         <v/>
@@ -12105,11 +11913,7 @@
     </row>
     <row r="27" ht="15.5" customHeight="1">
       <c r="A27" s="335" t="n"/>
-      <c r="B27" s="359" t="inlineStr">
-        <is>
-          <t>1.  Aruna Guggila</t>
-        </is>
-      </c>
+      <c r="B27" s="359" t="n"/>
       <c r="C27" s="161" t="n"/>
       <c r="D27" s="390" t="n"/>
       <c r="E27" s="161" t="n"/>
@@ -12123,11 +11927,7 @@
     </row>
     <row r="28" ht="15.5" customHeight="1">
       <c r="A28" s="335" t="n"/>
-      <c r="B28" s="365" t="inlineStr">
-        <is>
-          <t>2.  Krishna Guggila</t>
-        </is>
-      </c>
+      <c r="B28" s="365" t="n"/>
       <c r="C28" s="50" t="n"/>
       <c r="D28" s="392" t="n"/>
       <c r="E28" s="50" t="n"/>
@@ -12141,11 +11941,7 @@
     </row>
     <row r="29" ht="15.5" customHeight="1">
       <c r="A29" s="335" t="n"/>
-      <c r="B29" s="369" t="inlineStr">
-        <is>
-          <t>3.  Krupan Guggila</t>
-        </is>
-      </c>
+      <c r="B29" s="369" t="n"/>
       <c r="C29" s="292" t="n"/>
       <c r="D29" s="394" t="n"/>
       <c r="E29" s="292" t="n"/>
@@ -14598,11 +14394,6 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="C10" t="inlineStr">
@@ -14610,21 +14401,11 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>G Aruna</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
           <t>Director</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G Krupan </t>
         </is>
       </c>
     </row>
@@ -14665,16 +14446,6 @@
     </row>
     <row r="15">
       <c r="B15" s="297" t="n"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>A K Hardware Syndicate</t>
-        </is>
-      </c>
       <c r="F15" s="298" t="n"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -14684,16 +14455,6 @@
     </row>
     <row r="16">
       <c r="B16" s="297" t="n"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>G Krishna,G krupan</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>G K Infra Pvt Ltd</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Directors</t>
@@ -14761,11 +14522,7 @@
     </row>
     <row r="21">
       <c r="B21" s="297" t="n"/>
-      <c r="C21" s="193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G Krishna </t>
-        </is>
-      </c>
+      <c r="C21" s="193" t="n"/>
       <c r="D21" s="300" t="n"/>
       <c r="E21" s="733" t="n"/>
       <c r="F21" s="734" t="n"/>
@@ -14774,11 +14531,7 @@
     </row>
     <row r="22">
       <c r="B22" s="297" t="n"/>
-      <c r="C22" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G Krupan </t>
-        </is>
-      </c>
+      <c r="C22" s="73" t="n"/>
       <c r="D22" s="58" t="n"/>
       <c r="E22" s="734" t="n"/>
       <c r="F22" s="734" t="n"/>
@@ -14787,11 +14540,7 @@
     </row>
     <row r="23">
       <c r="B23" s="297" t="n"/>
-      <c r="C23" s="312" t="inlineStr">
-        <is>
-          <t>G Aruna</t>
-        </is>
-      </c>
+      <c r="C23" s="312" t="n"/>
       <c r="D23" s="263" t="n"/>
       <c r="E23" s="738" t="n"/>
       <c r="F23" s="738" t="n"/>
@@ -14925,34 +14674,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>( Firm regn. No. 000383S)</t>
-        </is>
-      </c>
-      <c r="G37" s="282" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="G37" s="282" t="n"/>
     </row>
     <row r="38">
       <c r="C38" s="294" t="n"/>
-      <c r="G38" s="282" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="G38" s="282" t="n"/>
     </row>
     <row r="39">
       <c r="G39" s="282" t="n"/>
     </row>
     <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Om Prakash Bang</t>
-        </is>
-      </c>
       <c r="G40" s="613" t="n"/>
     </row>
     <row r="41">
@@ -14968,28 +14699,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Membership No. 018948</t>
-        </is>
-      </c>
-      <c r="G42" s="282" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="G42" s="282" t="n"/>
     </row>
     <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Place: Hyderabad</t>
-        </is>
-      </c>
-      <c r="G43" s="282" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="G43" s="282" t="n"/>
     </row>
     <row r="44">
       <c r="C44">
@@ -15031,11 +14744,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="152" t="inlineStr">
-        <is>
-          <t>RAMSON AND GRANDSON JEWELLERS PRIVATE LIMITED</t>
-        </is>
-      </c>
+      <c r="A1" s="152" t="n"/>
       <c r="B1" s="146" t="n"/>
       <c r="C1" s="146" t="n"/>
       <c r="D1" s="146" t="n"/>
@@ -15737,11 +15446,6 @@
       <c r="F33" s="613" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>( Firm regn. No. 000383S)</t>
-        </is>
-      </c>
       <c r="B34" s="613" t="n"/>
       <c r="C34" s="613" t="n"/>
       <c r="D34" s="613" t="n"/>
@@ -15761,26 +15465,13 @@
     <row r="36">
       <c r="B36" s="613" t="n"/>
       <c r="C36" s="613" t="n"/>
-      <c r="D36" s="282" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="D36" s="282" t="n"/>
       <c r="F36" s="613" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Om Prakash Bang</t>
-        </is>
-      </c>
       <c r="B37" s="613" t="n"/>
       <c r="C37" s="613" t="n"/>
-      <c r="D37" s="282" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="D37" s="282" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15794,22 +15485,12 @@
       <c r="F38" s="613" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Membership No. 018948</t>
-        </is>
-      </c>
       <c r="B39" s="613" t="n"/>
       <c r="C39" s="613" t="n"/>
       <c r="D39" s="613" t="n"/>
       <c r="F39" s="613" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Place: Hyderabad</t>
-        </is>
-      </c>
       <c r="B40" s="613" t="n"/>
       <c r="C40" s="613" t="n"/>
       <c r="D40" s="282" t="inlineStr">
@@ -15820,28 +15501,15 @@
       <c r="F40" s="613" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Date : 21-09-2023</t>
-        </is>
-      </c>
       <c r="B41" s="613" t="n"/>
       <c r="C41" s="613" t="n"/>
-      <c r="D41" s="282" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="D41" s="282" t="n"/>
       <c r="F41" s="613" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="613" t="n"/>
       <c r="C42" s="613" t="n"/>
-      <c r="D42" s="282" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="D42" s="282" t="n"/>
       <c r="F42" s="613" t="n"/>
     </row>
     <row r="43">
@@ -15892,11 +15560,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="609" t="inlineStr">
-        <is>
-          <t>RAMSON AND GRANDSON JEWELLERS PRIVATE LIMITED</t>
-        </is>
-      </c>
+      <c r="A1" s="609" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="610" t="inlineStr">
@@ -16594,11 +16258,6 @@
       <c r="E45" s="746" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Firm regn. No. 000383S</t>
-        </is>
-      </c>
       <c r="C46" s="282" t="inlineStr">
         <is>
           <t>Director</t>
@@ -16607,28 +16266,15 @@
       <c r="E46" s="730" t="n"/>
     </row>
     <row r="47">
-      <c r="C47" s="282" t="inlineStr">
-        <is>
-          <t>G Krishna</t>
-        </is>
-      </c>
+      <c r="C47" s="282" t="n"/>
     </row>
     <row r="48">
-      <c r="C48" s="282" t="inlineStr">
-        <is>
-          <t>DIN: 03336421</t>
-        </is>
-      </c>
+      <c r="C48" s="282" t="n"/>
     </row>
     <row r="49">
       <c r="E49" s="283" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Om Prakash Bang</t>
-        </is>
-      </c>
       <c r="E50" s="766" t="n"/>
     </row>
     <row r="51">
@@ -16640,11 +16286,6 @@
       <c r="E51" s="766" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Membership No. 018948</t>
-        </is>
-      </c>
       <c r="C52" s="282" t="inlineStr">
         <is>
           <t>Director</t>
@@ -16653,27 +16294,14 @@
       <c r="E52" s="767" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Place: Hyderabad</t>
-        </is>
-      </c>
-      <c r="C53" s="282" t="inlineStr">
-        <is>
-          <t>G Krupan</t>
-        </is>
-      </c>
+      <c r="C53" s="282" t="n"/>
     </row>
     <row r="54">
       <c r="A54">
         <f>BS!A41</f>
         <v/>
       </c>
-      <c r="C54" s="282" t="inlineStr">
-        <is>
-          <t>DIN : 03363685</t>
-        </is>
-      </c>
+      <c r="C54" s="282" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
